--- a/artfynd/A 64131-2023 artfynd.xlsx
+++ b/artfynd/A 64131-2023 artfynd.xlsx
@@ -1397,11 +1397,11 @@
         <v>120664424</v>
       </c>
       <c r="B9" t="n">
-        <v>91119</v>
+        <v>91168</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">

--- a/artfynd/A 64131-2023 artfynd.xlsx
+++ b/artfynd/A 64131-2023 artfynd.xlsx
@@ -1397,7 +1397,7 @@
         <v>120664424</v>
       </c>
       <c r="B9" t="n">
-        <v>91168</v>
+        <v>91182</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 64131-2023 artfynd.xlsx
+++ b/artfynd/A 64131-2023 artfynd.xlsx
@@ -1397,7 +1397,7 @@
         <v>120664424</v>
       </c>
       <c r="B9" t="n">
-        <v>91182</v>
+        <v>91184</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 64131-2023 artfynd.xlsx
+++ b/artfynd/A 64131-2023 artfynd.xlsx
@@ -1397,7 +1397,7 @@
         <v>120664424</v>
       </c>
       <c r="B9" t="n">
-        <v>91184</v>
+        <v>91185</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 64131-2023 artfynd.xlsx
+++ b/artfynd/A 64131-2023 artfynd.xlsx
@@ -1397,7 +1397,7 @@
         <v>120664424</v>
       </c>
       <c r="B9" t="n">
-        <v>91185</v>
+        <v>91194</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 64131-2023 artfynd.xlsx
+++ b/artfynd/A 64131-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120665106</v>
+        <v>120665599</v>
       </c>
       <c r="B2" t="n">
-        <v>57501</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Noret, Noret, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>618388</v>
+        <v>618498</v>
       </c>
       <c r="R2" t="n">
-        <v>7011435</v>
+        <v>7011467</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120668758</v>
+        <v>120665833</v>
       </c>
       <c r="B3" t="n">
-        <v>90965</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,28 +792,28 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skedomssjön, Ång</t>
+          <t>Noret, Noret, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>618515</v>
+        <v>618505</v>
       </c>
       <c r="R3" t="n">
-        <v>7011455</v>
+        <v>7011493</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120668759</v>
+        <v>120668755</v>
       </c>
       <c r="B4" t="n">
-        <v>90965</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,12 +889,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618498</v>
+        <v>618465</v>
       </c>
       <c r="R4" t="n">
-        <v>7011456</v>
+        <v>7011544</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -986,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120668768</v>
+        <v>120668757</v>
       </c>
       <c r="B5" t="n">
-        <v>98056</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618417</v>
+        <v>618510</v>
       </c>
       <c r="R5" t="n">
-        <v>7011427</v>
+        <v>7011513</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1088,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120668773</v>
+        <v>120668758</v>
       </c>
       <c r="B6" t="n">
-        <v>105161</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618379</v>
+        <v>618515</v>
       </c>
       <c r="R6" t="n">
-        <v>7011431</v>
+        <v>7011455</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1190,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120668753</v>
+        <v>120668759</v>
       </c>
       <c r="B7" t="n">
-        <v>91119</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618382</v>
+        <v>618498</v>
       </c>
       <c r="R7" t="n">
-        <v>7011403</v>
+        <v>7011456</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1292,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120668762</v>
+        <v>120668760</v>
       </c>
       <c r="B8" t="n">
-        <v>90965</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1317,12 +1277,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618375</v>
+        <v>618436</v>
       </c>
       <c r="R8" t="n">
-        <v>7011382</v>
+        <v>7011432</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1394,53 +1354,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120664424</v>
+        <v>120668761</v>
       </c>
       <c r="B9" t="n">
-        <v>91194</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Noret, Noret, Ång</t>
+          <t>Skedomssjön, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>618381</v>
+        <v>618435</v>
       </c>
       <c r="R9" t="n">
-        <v>7011324</v>
+        <v>7011425</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1496,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120665599</v>
+        <v>120668762</v>
       </c>
       <c r="B10" t="n">
-        <v>90965</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1521,28 +1471,28 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Noret, Noret, Ång</t>
+          <t>Skedomssjön, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>618498</v>
+        <v>618375</v>
       </c>
       <c r="R10" t="n">
-        <v>7011467</v>
+        <v>7011382</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1598,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120668748</v>
+        <v>120668763</v>
       </c>
       <c r="B11" t="n">
-        <v>90644</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>618514</v>
+        <v>618355</v>
       </c>
       <c r="R11" t="n">
-        <v>7011506</v>
+        <v>7011365</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1700,53 +1645,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120665039</v>
+        <v>120668764</v>
       </c>
       <c r="B12" t="n">
-        <v>91119</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Noret, Noret, Ång</t>
+          <t>Skedomssjön, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>618372</v>
+        <v>618322</v>
       </c>
       <c r="R12" t="n">
-        <v>7011390</v>
+        <v>7011382</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1802,37 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120668750</v>
+        <v>120668752</v>
       </c>
       <c r="B13" t="n">
-        <v>90644</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>618434</v>
+        <v>618376</v>
       </c>
       <c r="R13" t="n">
-        <v>7011286</v>
+        <v>7011388</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1904,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120668766</v>
+        <v>120664424</v>
       </c>
       <c r="B14" t="n">
-        <v>79675</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1920,37 +1850,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skedomssjön, Ång</t>
+          <t>Noret, Noret, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
         <v>618381</v>
       </c>
       <c r="R14" t="n">
-        <v>7011335</v>
+        <v>7011324</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2006,37 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120665331</v>
+        <v>120665039</v>
       </c>
       <c r="B15" t="n">
-        <v>98056</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,13 +1971,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>618420</v>
+        <v>618372</v>
       </c>
       <c r="R15" t="n">
-        <v>7011408</v>
+        <v>7011390</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2108,15 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120665833</v>
+        <v>120668753</v>
       </c>
       <c r="B16" t="n">
-        <v>90965</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2124,37 +2044,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Noret, Noret, Ång</t>
+          <t>Skedomssjön, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>618505</v>
+        <v>618382</v>
       </c>
       <c r="R16" t="n">
-        <v>7011493</v>
+        <v>7011403</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2210,15 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120668763</v>
+        <v>120668754</v>
       </c>
       <c r="B17" t="n">
-        <v>90965</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>618355</v>
+        <v>618376</v>
       </c>
       <c r="R17" t="n">
-        <v>7011365</v>
+        <v>7011324</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2312,37 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120668752</v>
+        <v>120668748</v>
       </c>
       <c r="B18" t="n">
-        <v>90679</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>618376</v>
+        <v>618514</v>
       </c>
       <c r="R18" t="n">
-        <v>7011388</v>
+        <v>7011506</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2414,15 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120668772</v>
+        <v>120668750</v>
       </c>
       <c r="B19" t="n">
-        <v>105161</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2430,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>618386</v>
+        <v>618434</v>
       </c>
       <c r="R19" t="n">
-        <v>7011441</v>
+        <v>7011286</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2516,15 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120668761</v>
+        <v>120668766</v>
       </c>
       <c r="B20" t="n">
-        <v>90965</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2532,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>618435</v>
+        <v>618381</v>
       </c>
       <c r="R20" t="n">
-        <v>7011425</v>
+        <v>7011335</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2618,53 +2518,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120666049</v>
+        <v>120665106</v>
       </c>
       <c r="B21" t="n">
-        <v>98056</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Noret, Noret, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>618442</v>
+        <v>618388</v>
       </c>
       <c r="R21" t="n">
-        <v>7011611</v>
+        <v>7011435</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2720,53 +2620,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120668755</v>
+        <v>120665331</v>
       </c>
       <c r="B22" t="n">
-        <v>90965</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skedomssjön, Ång</t>
+          <t>Noret, Noret, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>618465</v>
+        <v>618420</v>
       </c>
       <c r="R22" t="n">
-        <v>7011544</v>
+        <v>7011408</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2822,53 +2717,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120668757</v>
+        <v>120666049</v>
       </c>
       <c r="B23" t="n">
-        <v>90965</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skedomssjön, Ång</t>
+          <t>Noret, Noret, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>618510</v>
+        <v>618442</v>
       </c>
       <c r="R23" t="n">
-        <v>7011513</v>
+        <v>7011611</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2924,15 +2814,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120668754</v>
+        <v>120668768</v>
       </c>
       <c r="B24" t="n">
-        <v>91119</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2940,21 +2825,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>618376</v>
+        <v>618417</v>
       </c>
       <c r="R24" t="n">
-        <v>7011324</v>
+        <v>7011427</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3026,37 +2911,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120668760</v>
+        <v>120668772</v>
       </c>
       <c r="B25" t="n">
-        <v>90965</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>618436</v>
+        <v>618386</v>
       </c>
       <c r="R25" t="n">
-        <v>7011432</v>
+        <v>7011441</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3128,37 +3008,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120668764</v>
+        <v>120668773</v>
       </c>
       <c r="B26" t="n">
-        <v>90965</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3043,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>618322</v>
+        <v>618379</v>
       </c>
       <c r="R26" t="n">
-        <v>7011382</v>
+        <v>7011431</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3227,6 +3102,103 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120668775</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Skedomssjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>618403</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7011633</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Multrå</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64131-2023 artfynd.xlsx
+++ b/artfynd/A 64131-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120665599</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120665833</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120668755</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120668757</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120668758</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120668759</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120668760</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120668761</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120668762</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120668763</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120668764</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120668752</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120664424</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120665039</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120668753</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120668754</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120668748</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120668750</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120668766</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2617,6 +2717,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120665106</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2714,6 +2819,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120665331</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2811,6 +2921,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120666049</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2908,6 +3023,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120668768</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3005,6 +3125,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120668772</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3102,6 +3227,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120668773</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3199,8 +3329,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120668775</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>